--- a/exports/trend_1d/ICICIBANK_full_report.xlsx
+++ b/exports/trend_1d/ICICIBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:U92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42034</v>
+        <v>42037</v>
       </c>
       <c r="H2" t="n">
-        <v>327.91</v>
+        <v>319.86</v>
       </c>
       <c r="I2" t="n">
         <v>325.016139962853</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>2.23</v>
+        <v>-0.28</v>
       </c>
       <c r="L2" t="n">
         <v>1.53</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.81</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42122</v>
+        <v>42123</v>
       </c>
       <c r="H3" t="n">
-        <v>297.14</v>
+        <v>300.14</v>
       </c>
       <c r="I3" t="n">
         <v>299.8993093355762</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="n">
-        <v>7.1</v>
+        <v>6.17</v>
       </c>
       <c r="L3" t="n">
         <v>2.89</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H4" t="n">
-        <v>276.82</v>
+        <v>268.86</v>
       </c>
       <c r="I4" t="n">
         <v>273.9675451449285</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.77</v>
+        <v>-10.42</v>
       </c>
       <c r="L4" t="n">
-        <v>8.949999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="M4" t="n">
         <v>0.73</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>8.98</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42174</v>
+        <v>42177</v>
       </c>
       <c r="H5" t="n">
-        <v>276.86</v>
+        <v>286.41</v>
       </c>
       <c r="I5" t="n">
         <v>279.7066301733764</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.98</v>
+        <v>-6.53</v>
       </c>
       <c r="L5" t="n">
-        <v>3.47</v>
+        <v>6.81</v>
       </c>
       <c r="M5" t="n">
         <v>1.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.59</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
         <v>-2.88</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42208</v>
+        <v>42209</v>
       </c>
       <c r="H6" t="n">
-        <v>284.45</v>
+        <v>273.27</v>
       </c>
       <c r="I6" t="n">
         <v>274.0302084585712</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.68</v>
+        <v>-4.59</v>
       </c>
       <c r="L6" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
         <v>3.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.62</v>
+        <v>3.93</v>
       </c>
       <c r="O6" t="n">
         <v>3.45</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.56</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42216</v>
+        <v>42219</v>
       </c>
       <c r="H7" t="n">
-        <v>274.9</v>
+        <v>284.45</v>
       </c>
       <c r="I7" t="n">
         <v>281.6747205620704</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6</v>
+        <v>-4.09</v>
       </c>
       <c r="L7" t="n">
-        <v>3.73</v>
+        <v>4.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.18</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.67</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H8" t="n">
-        <v>269.55</v>
+        <v>245.41</v>
       </c>
       <c r="I8" t="n">
         <v>261.3663862053031</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.24</v>
+        <v>-13.72</v>
       </c>
       <c r="L8" t="n">
-        <v>7.77</v>
+        <v>14.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.51</v>
+        <v>4.76</v>
       </c>
       <c r="N8" t="n">
-        <v>3.51</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>3.47</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>14.07</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42286</v>
+        <v>42289</v>
       </c>
       <c r="H9" t="n">
-        <v>260.09</v>
+        <v>261.45</v>
       </c>
       <c r="I9" t="n">
         <v>260.394351206725</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.98</v>
+        <v>-6.54</v>
       </c>
       <c r="L9" t="n">
-        <v>7.17</v>
+        <v>7.98</v>
       </c>
       <c r="M9" t="n">
         <v>2.74</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>8.74</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H10" t="n">
-        <v>242.82</v>
+        <v>239.22</v>
       </c>
       <c r="I10" t="n">
         <v>241.0391207077292</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.13</v>
+        <v>-8.5</v>
       </c>
       <c r="L10" t="n">
-        <v>7.94</v>
+        <v>10.98</v>
       </c>
       <c r="M10" t="n">
-        <v>1.39</v>
+        <v>2.92</v>
       </c>
       <c r="N10" t="n">
         <v>4.4</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>7.19</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H11" t="n">
-        <v>186.32</v>
+        <v>200</v>
       </c>
       <c r="I11" t="n">
         <v>188.397421478237</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K11" t="n">
-        <v>22.11</v>
+        <v>16.39</v>
       </c>
       <c r="L11" t="n">
         <v>5.46</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>3.29</v>
       </c>
       <c r="N11" t="n">
         <v>7.84</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>15.44</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42489</v>
+        <v>42492</v>
       </c>
       <c r="H12" t="n">
-        <v>215.41</v>
+        <v>206.14</v>
       </c>
       <c r="I12" t="n">
         <v>207.094106380589</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K12" t="n">
-        <v>7.7</v>
+        <v>3.07</v>
       </c>
       <c r="L12" t="n">
         <v>4.53</v>
       </c>
       <c r="M12" t="n">
-        <v>1.87</v>
+        <v>4.07</v>
       </c>
       <c r="N12" t="n">
         <v>5.51</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>12.96</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42516</v>
+        <v>42517</v>
       </c>
       <c r="H13" t="n">
-        <v>219.23</v>
+        <v>221.05</v>
       </c>
       <c r="I13" t="n">
         <v>220.9491575961641</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.35</v>
+        <v>-7.23</v>
       </c>
       <c r="L13" t="n">
-        <v>7.17</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>2.03</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>9.57</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42544</v>
+        <v>42545</v>
       </c>
       <c r="H14" t="n">
-        <v>219</v>
+        <v>209.95</v>
       </c>
       <c r="I14" t="n">
         <v>213.5491386736931</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.93</v>
+        <v>-5.02</v>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>9.07</v>
       </c>
       <c r="M14" t="n">
-        <v>2.01</v>
+        <v>4.94</v>
       </c>
       <c r="N14" t="n">
-        <v>3.59</v>
+        <v>4.13</v>
       </c>
       <c r="O14" t="n">
         <v>0.83</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.77</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42562</v>
+        <v>42563</v>
       </c>
       <c r="H15" t="n">
-        <v>227.14</v>
+        <v>237.91</v>
       </c>
       <c r="I15" t="n">
         <v>228.3650105572277</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.19</v>
+        <v>-13.32</v>
       </c>
       <c r="L15" t="n">
-        <v>8.73</v>
+        <v>13.53</v>
       </c>
       <c r="M15" t="n">
         <v>1.92</v>
       </c>
       <c r="N15" t="n">
-        <v>3.27</v>
+        <v>4.74</v>
       </c>
       <c r="O15" t="n">
         <v>-4.13</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>10.21</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42583</v>
+        <v>42584</v>
       </c>
       <c r="H16" t="n">
-        <v>226.82</v>
+        <v>223</v>
       </c>
       <c r="I16" t="n">
         <v>226.8010850177406</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.66</v>
+        <v>-6.27</v>
       </c>
       <c r="L16" t="n">
-        <v>5.16</v>
+        <v>6.38</v>
       </c>
       <c r="M16" t="n">
         <v>2.66</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>10.7</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42615</v>
+        <v>42619</v>
       </c>
       <c r="H17" t="n">
-        <v>237.55</v>
+        <v>247.91</v>
       </c>
       <c r="I17" t="n">
         <v>238.1268584839222</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.52</v>
+        <v>-11.17</v>
       </c>
       <c r="L17" t="n">
-        <v>7.74</v>
+        <v>11.66</v>
       </c>
       <c r="M17" t="n">
         <v>1.56</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>4.36</v>
       </c>
       <c r="O17" t="n">
         <v>-1.68</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>8.66</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H18" t="n">
-        <v>237.05</v>
+        <v>227.59</v>
       </c>
       <c r="I18" t="n">
         <v>234.4328326008011</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.38</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>5.03</v>
+        <v>10.78</v>
       </c>
       <c r="M18" t="n">
         <v>2.59</v>
       </c>
       <c r="N18" t="n">
-        <v>3.21</v>
+        <v>3.99</v>
       </c>
       <c r="O18" t="n">
         <v>4.36</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.68</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42660</v>
+        <v>42661</v>
       </c>
       <c r="H19" t="n">
-        <v>235.23</v>
+        <v>245.77</v>
       </c>
       <c r="I19" t="n">
         <v>238.1108470149133</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.36</v>
+        <v>-7.99</v>
       </c>
       <c r="L19" t="n">
-        <v>5.26</v>
+        <v>8.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.76</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.19</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42692</v>
+        <v>42695</v>
       </c>
       <c r="H20" t="n">
-        <v>240.55</v>
+        <v>237.45</v>
       </c>
       <c r="I20" t="n">
         <v>238.5706149953927</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.12</v>
+        <v>-3.39</v>
       </c>
       <c r="L20" t="n">
         <v>9.369999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.71</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42746</v>
+        <v>42747</v>
       </c>
       <c r="H21" t="n">
-        <v>240.64</v>
+        <v>243.95</v>
       </c>
       <c r="I21" t="n">
         <v>242.9723747529807</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.34</v>
+        <v>-2.74</v>
       </c>
       <c r="L21" t="n">
         <v>3.29</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.55</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42815</v>
+        <v>42816</v>
       </c>
       <c r="H22" t="n">
-        <v>247.32</v>
+        <v>240.91</v>
       </c>
       <c r="I22" t="n">
         <v>241.6848059605642</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K22" t="n">
-        <v>1.38</v>
+        <v>-1.25</v>
       </c>
       <c r="L22" t="n">
         <v>4.92</v>
       </c>
       <c r="M22" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="N22" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="O22" t="n">
         <v>1.38</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42825</v>
+        <v>42828</v>
       </c>
       <c r="H23" t="n">
-        <v>251.68</v>
+        <v>260.64</v>
       </c>
       <c r="I23" t="n">
         <v>259.2455233755118</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.47</v>
+        <v>-8.19</v>
       </c>
       <c r="L23" t="n">
-        <v>6.89</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>1.91</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>3.56</v>
       </c>
       <c r="O23" t="n">
         <v>-2.59</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.59</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H24" t="n">
-        <v>295.5</v>
+        <v>290.6</v>
       </c>
       <c r="I24" t="n">
         <v>291.674481960148</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K24" t="n">
-        <v>13.37</v>
+        <v>11.49</v>
       </c>
       <c r="L24" t="n">
         <v>7.5</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.18</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H25" t="n">
-        <v>266.55</v>
+        <v>305.7</v>
       </c>
       <c r="I25" t="n">
         <v>278.9057529486925</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K25" t="n">
-        <v>8.279999999999999</v>
+        <v>-5.2</v>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>6.95</v>
       </c>
       <c r="M25" t="n">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>1.69</v>
+        <v>14.69</v>
       </c>
       <c r="O25" t="n">
         <v>-1.66</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43133</v>
+        <v>43136</v>
       </c>
       <c r="H26" t="n">
-        <v>335.1</v>
+        <v>329.7</v>
       </c>
       <c r="I26" t="n">
         <v>331.5186500887793</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K26" t="n">
-        <v>9.619999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="L26" t="n">
         <v>6.98</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>9.27</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="H27" t="n">
-        <v>289.8</v>
+        <v>309.3</v>
       </c>
       <c r="I27" t="n">
         <v>293.8314457974002</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K27" t="n">
-        <v>12.1</v>
+        <v>6.19</v>
       </c>
       <c r="L27" t="n">
         <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>2.63</v>
+        <v>4.21</v>
       </c>
       <c r="N27" t="n">
-        <v>3.72</v>
+        <v>6.73</v>
       </c>
       <c r="O27" t="n">
         <v>-1.61</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.35</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H28" t="n">
-        <v>286.75</v>
+        <v>284.1</v>
       </c>
       <c r="I28" t="n">
         <v>284.3877080210062</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.29</v>
+        <v>-8.15</v>
       </c>
       <c r="L28" t="n">
         <v>9.699999999999999</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H29" t="n">
-        <v>274.65</v>
+        <v>285.65</v>
       </c>
       <c r="I29" t="n">
         <v>282.4368267533299</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K29" t="n">
-        <v>3.33</v>
+        <v>-0.55</v>
       </c>
       <c r="L29" t="n">
         <v>6.55</v>
@@ -2094,7 +2441,7 @@
         <v>1.43</v>
       </c>
       <c r="N29" t="n">
-        <v>3.72</v>
+        <v>4.01</v>
       </c>
       <c r="O29" t="n">
         <v>-0.92</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.75</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H30" t="n">
-        <v>317.1</v>
+        <v>308.75</v>
       </c>
       <c r="I30" t="n">
         <v>316.1896019762219</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K30" t="n">
-        <v>11.01</v>
+        <v>8.09</v>
       </c>
       <c r="L30" t="n">
         <v>4.34</v>
@@ -2151,7 +2510,7 @@
         <v>1.44</v>
       </c>
       <c r="N30" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="O30" t="n">
         <v>4.01</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>11.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43399</v>
+        <v>43402</v>
       </c>
       <c r="H31" t="n">
-        <v>315.65</v>
+        <v>349.4</v>
       </c>
       <c r="I31" t="n">
         <v>338.7584617059662</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.23</v>
+        <v>-13.17</v>
       </c>
       <c r="L31" t="n">
-        <v>6.88</v>
+        <v>14.32</v>
       </c>
       <c r="M31" t="n">
-        <v>1.83</v>
+        <v>4.23</v>
       </c>
       <c r="N31" t="n">
-        <v>4.44</v>
+        <v>10.69</v>
       </c>
       <c r="O31" t="n">
         <v>-2.63</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>15.44</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H32" t="n">
-        <v>357.2</v>
+        <v>343.55</v>
       </c>
       <c r="I32" t="n">
         <v>354.9914128295948</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K32" t="n">
-        <v>2.23</v>
+        <v>-1.67</v>
       </c>
       <c r="L32" t="n">
         <v>6.04</v>
@@ -2265,7 +2648,7 @@
         <v>2.58</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>3.82</v>
       </c>
       <c r="O32" t="n">
         <v>10.69</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43529</v>
+        <v>43530</v>
       </c>
       <c r="H33" t="n">
-        <v>363.25</v>
+        <v>371.95</v>
       </c>
       <c r="I33" t="n">
         <v>367.3066750982775</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.73</v>
+        <v>-8.27</v>
       </c>
       <c r="L33" t="n">
         <v>9.630000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H34" t="n">
-        <v>385.1</v>
+        <v>376.3</v>
       </c>
       <c r="I34" t="n">
         <v>380.7694809249375</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K34" t="n">
-        <v>3.54</v>
+        <v>1.17</v>
       </c>
       <c r="L34" t="n">
         <v>1.8</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43607</v>
+        <v>43608</v>
       </c>
       <c r="H35" t="n">
-        <v>405.35</v>
+        <v>410.85</v>
       </c>
       <c r="I35" t="n">
         <v>410.5158165605587</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.72</v>
+        <v>-9.18</v>
       </c>
       <c r="L35" t="n">
-        <v>10.02</v>
+        <v>13.73</v>
       </c>
       <c r="M35" t="n">
         <v>3.99</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.42</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H36" t="n">
-        <v>418.65</v>
+        <v>410.3</v>
       </c>
       <c r="I36" t="n">
         <v>414.5572614067376</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K36" t="n">
-        <v>1.9</v>
+        <v>-0.13</v>
       </c>
       <c r="L36" t="n">
         <v>0.84</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>6.93</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H37" t="n">
-        <v>417.5</v>
+        <v>446.3</v>
       </c>
       <c r="I37" t="n">
         <v>424.3889338245288</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.75</v>
+        <v>-8.77</v>
       </c>
       <c r="L37" t="n">
-        <v>6.92</v>
+        <v>9.68</v>
       </c>
       <c r="M37" t="n">
-        <v>4.15</v>
+        <v>4.38</v>
       </c>
       <c r="N37" t="n">
         <v>7.99</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.27</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H38" t="n">
-        <v>525.65</v>
+        <v>504.6</v>
       </c>
       <c r="I38" t="n">
         <v>521.2334472524702</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K38" t="n">
-        <v>17.78</v>
+        <v>13.06</v>
       </c>
       <c r="L38" t="n">
         <v>7.8</v>
@@ -2607,7 +3062,7 @@
         <v>1.53</v>
       </c>
       <c r="N38" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
         <v>6.9</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43872</v>
+        <v>43873</v>
       </c>
       <c r="H39" t="n">
-        <v>539.75</v>
+        <v>549.3</v>
       </c>
       <c r="I39" t="n">
         <v>548.9571538388909</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.97</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>8.4</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="N39" t="n">
         <v>2.96</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.14</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H40" t="n">
-        <v>515.35</v>
+        <v>497.25</v>
       </c>
       <c r="I40" t="n">
         <v>514.0347888538402</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.18</v>
+        <v>-9.48</v>
       </c>
       <c r="L40" t="n">
-        <v>6.67</v>
+        <v>10.4</v>
       </c>
       <c r="M40" t="n">
-        <v>1.37</v>
+        <v>2.67</v>
       </c>
       <c r="N40" t="n">
-        <v>3.14</v>
+        <v>3.51</v>
       </c>
       <c r="O40" t="n">
         <v>1.77</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.99</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H41" t="n">
-        <v>348.4</v>
+        <v>356.85</v>
       </c>
       <c r="I41" t="n">
         <v>349.2879403858748</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K41" t="n">
-        <v>29.93</v>
+        <v>28.24</v>
       </c>
       <c r="L41" t="n">
         <v>4.69</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>13.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44041</v>
+        <v>44042</v>
       </c>
       <c r="H42" t="n">
-        <v>351.05</v>
+        <v>344.95</v>
       </c>
       <c r="I42" t="n">
         <v>346.4598859826581</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.63</v>
+        <v>-3.33</v>
       </c>
       <c r="L42" t="n">
         <v>9.18</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>14.07</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44068</v>
+        <v>44069</v>
       </c>
       <c r="H43" t="n">
-        <v>386.35</v>
+        <v>389.35</v>
       </c>
       <c r="I43" t="n">
         <v>387.7889082151412</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>-12</v>
+        <v>-12.87</v>
       </c>
       <c r="L43" t="n">
-        <v>13</v>
+        <v>13.54</v>
       </c>
       <c r="M43" t="n">
         <v>1.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H44" t="n">
-        <v>375.7</v>
+        <v>367.6</v>
       </c>
       <c r="I44" t="n">
         <v>369.3426570734915</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.51</v>
+        <v>-5.59</v>
       </c>
       <c r="L44" t="n">
-        <v>5.39</v>
+        <v>7.05</v>
       </c>
       <c r="M44" t="n">
         <v>2.02</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.35</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H45" t="n">
-        <v>373.1</v>
+        <v>380.6</v>
       </c>
       <c r="I45" t="n">
         <v>378.2736107857879</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.5</v>
+        <v>-3.54</v>
       </c>
       <c r="L45" t="n">
         <v>4.09</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>10.31</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H46" t="n">
-        <v>628</v>
+        <v>597.75</v>
       </c>
       <c r="I46" t="n">
         <v>605.732462548372</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K46" t="n">
-        <v>65</v>
+        <v>57.05</v>
       </c>
       <c r="L46" t="n">
         <v>1.71</v>
       </c>
       <c r="M46" t="n">
-        <v>1.54</v>
+        <v>2.07</v>
       </c>
       <c r="N46" t="n">
-        <v>4.38</v>
+        <v>4.82</v>
       </c>
       <c r="O46" t="n">
         <v>2.01</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.29</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44313</v>
+        <v>44314</v>
       </c>
       <c r="H47" t="n">
-        <v>598.75</v>
+        <v>621.35</v>
       </c>
       <c r="I47" t="n">
         <v>599.9987156459194</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.17</v>
+        <v>-3.95</v>
       </c>
       <c r="L47" t="n">
         <v>6.73</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.32</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44515</v>
+        <v>44516</v>
       </c>
       <c r="H48" t="n">
-        <v>773.3</v>
+        <v>764.05</v>
       </c>
       <c r="I48" t="n">
         <v>764.1809847221625</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K48" t="n">
-        <v>24.45</v>
+        <v>22.97</v>
       </c>
       <c r="L48" t="n">
         <v>5.9</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>8</v>
+      </c>
+      <c r="U48" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.49</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H49" t="n">
-        <v>764.7</v>
+        <v>772.85</v>
       </c>
       <c r="I49" t="n">
         <v>765.5908913378021</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.09</v>
+        <v>-1.15</v>
       </c>
       <c r="L49" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="M49" t="n">
         <v>1.8</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.64</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H50" t="n">
-        <v>790.8</v>
+        <v>753.7</v>
       </c>
       <c r="I50" t="n">
         <v>779.174614064367</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>2.32</v>
+        <v>-2.48</v>
       </c>
       <c r="L50" t="n">
-        <v>1.2</v>
+        <v>2.81</v>
       </c>
       <c r="M50" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="N50" t="n">
-        <v>2.32</v>
+        <v>4.69</v>
       </c>
       <c r="O50" t="n">
         <v>1.07</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.01</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H51" t="n">
-        <v>730.3</v>
+        <v>736.25</v>
       </c>
       <c r="I51" t="n">
         <v>735.1393086485741</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K51" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="L51" t="n">
         <v>3.22</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>7.96</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H52" t="n">
-        <v>719.25</v>
+        <v>710.35</v>
       </c>
       <c r="I52" t="n">
         <v>716.8398634241885</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.31</v>
+        <v>-3.52</v>
       </c>
       <c r="L52" t="n">
-        <v>3.52</v>
+        <v>4.32</v>
       </c>
       <c r="M52" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="N52" t="n">
         <v>2.26</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.75</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44707</v>
+        <v>44708</v>
       </c>
       <c r="H53" t="n">
-        <v>728.5</v>
+        <v>739.8</v>
       </c>
       <c r="I53" t="n">
         <v>737.4945760125449</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.56</v>
+        <v>-4.15</v>
       </c>
       <c r="L53" t="n">
-        <v>3.19</v>
+        <v>4.34</v>
       </c>
       <c r="M53" t="n">
         <v>1.35</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.5</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44722</v>
+        <v>44725</v>
       </c>
       <c r="H54" t="n">
-        <v>720</v>
+        <v>688</v>
       </c>
       <c r="I54" t="n">
         <v>702.4609245938672</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.68</v>
+        <v>-7</v>
       </c>
       <c r="L54" t="n">
-        <v>2.95</v>
+        <v>7.8</v>
       </c>
       <c r="M54" t="n">
-        <v>1.09</v>
+        <v>2.47</v>
       </c>
       <c r="N54" t="n">
-        <v>1.74</v>
+        <v>4.44</v>
       </c>
       <c r="O54" t="n">
         <v>1.55</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H55" t="n">
-        <v>725.95</v>
+        <v>742</v>
       </c>
       <c r="I55" t="n">
         <v>732.9446891384555</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.52</v>
+        <v>-7.85</v>
       </c>
       <c r="L55" t="n">
-        <v>6.42</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>2.16</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.57</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H56" t="n">
-        <v>882.25</v>
+        <v>861.05</v>
       </c>
       <c r="I56" t="n">
         <v>875.5550290796115</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K56" t="n">
-        <v>18.9</v>
+        <v>16.04</v>
       </c>
       <c r="L56" t="n">
         <v>1.21</v>
@@ -3633,7 +4304,7 @@
         <v>2.74</v>
       </c>
       <c r="N56" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O56" t="n">
         <v>2.21</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.27</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44855</v>
+        <v>44858</v>
       </c>
       <c r="H57" t="n">
-        <v>907.15</v>
+        <v>926.3</v>
       </c>
       <c r="I57" t="n">
         <v>909.266091559961</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.35</v>
+        <v>-7.58</v>
       </c>
       <c r="L57" t="n">
-        <v>5.68</v>
+        <v>8.41</v>
       </c>
       <c r="M57" t="n">
         <v>3.54</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.44</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H58" t="n">
-        <v>908.8</v>
+        <v>902</v>
       </c>
       <c r="I58" t="n">
         <v>904.6891286713666</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.89</v>
+        <v>-2.62</v>
       </c>
       <c r="L58" t="n">
         <v>3.78</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.99</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H59" t="n">
-        <v>867.75</v>
+        <v>872.1</v>
       </c>
       <c r="I59" t="n">
         <v>871.7759103163892</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K59" t="n">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="L59" t="n">
         <v>2.37</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.64</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H60" t="n">
-        <v>964.1</v>
+        <v>952.85</v>
       </c>
       <c r="I60" t="n">
         <v>953.1378342237454</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K60" t="n">
-        <v>10.55</v>
+        <v>9.26</v>
       </c>
       <c r="L60" t="n">
         <v>7.09</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.26</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H61" t="n">
-        <v>946.7</v>
+        <v>991.2</v>
       </c>
       <c r="I61" t="n">
         <v>950.8190950355374</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K61" t="n">
-        <v>0.65</v>
+        <v>-4.02</v>
       </c>
       <c r="L61" t="n">
         <v>4.69</v>
       </c>
       <c r="M61" t="n">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="N61" t="n">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="O61" t="n">
         <v>-1.17</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.13</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45292</v>
+        <v>45293</v>
       </c>
       <c r="H62" t="n">
-        <v>999.4</v>
+        <v>982.25</v>
       </c>
       <c r="I62" t="n">
         <v>983.9148533250376</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>0.83</v>
+        <v>-0.9</v>
       </c>
       <c r="L62" t="n">
         <v>3.01</v>
@@ -3975,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="O62" t="n">
         <v>4.7</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.54</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H63" t="n">
-        <v>1008.7</v>
+        <v>1029.05</v>
       </c>
       <c r="I63" t="n">
         <v>1028.40216672556</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.69</v>
+        <v>-4.76</v>
       </c>
       <c r="L63" t="n">
-        <v>3.42</v>
+        <v>7.85</v>
       </c>
       <c r="M63" t="n">
-        <v>0.68</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="O63" t="n">
         <v>-1.72</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.19</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H64" t="n">
-        <v>1067.05</v>
+        <v>1055.45</v>
       </c>
       <c r="I64" t="n">
         <v>1056.231180306748</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K64" t="n">
-        <v>3.69</v>
+        <v>2.57</v>
       </c>
       <c r="L64" t="n">
         <v>4.26</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.43</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H65" t="n">
-        <v>1107.9</v>
+        <v>1160.15</v>
       </c>
       <c r="I65" t="n">
         <v>1120.348523340668</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.97</v>
+        <v>-9.92</v>
       </c>
       <c r="L65" t="n">
-        <v>6.65</v>
+        <v>10.23</v>
       </c>
       <c r="M65" t="n">
         <v>1.23</v>
       </c>
       <c r="N65" t="n">
-        <v>1.82</v>
+        <v>4.72</v>
       </c>
       <c r="O65" t="n">
         <v>-1.09</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.26</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H66" t="n">
-        <v>1160</v>
+        <v>1071.45</v>
       </c>
       <c r="I66" t="n">
         <v>1087.136895276581</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.01</v>
+        <v>-7.65</v>
       </c>
       <c r="L66" t="n">
-        <v>5.45</v>
+        <v>9.19</v>
       </c>
       <c r="M66" t="n">
         <v>1.06</v>
       </c>
       <c r="N66" t="n">
-        <v>2.21</v>
+        <v>7.63</v>
       </c>
       <c r="O66" t="n">
         <v>4.72</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>12.19</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45467</v>
+        <v>45468</v>
       </c>
       <c r="H67" t="n">
-        <v>1170.1</v>
+        <v>1197.95</v>
       </c>
       <c r="I67" t="n">
         <v>1188.029151714447</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.81</v>
       </c>
       <c r="L67" t="n">
-        <v>9.73</v>
+        <v>12.56</v>
       </c>
       <c r="M67" t="n">
         <v>1.26</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H68" t="n">
-        <v>1196.55</v>
+        <v>1172.6</v>
       </c>
       <c r="I68" t="n">
         <v>1176.322888198966</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.12</v>
+        <v>-2.12</v>
       </c>
       <c r="L68" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="M68" t="n">
         <v>1.43</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>6.86</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45533</v>
+        <v>45534</v>
       </c>
       <c r="H69" t="n">
-        <v>1221.9</v>
+        <v>1229.2</v>
       </c>
       <c r="I69" t="n">
         <v>1228.938060418206</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.2</v>
+        <v>-4.83</v>
       </c>
       <c r="L69" t="n">
-        <v>5.32</v>
+        <v>5.37</v>
       </c>
       <c r="M69" t="n">
         <v>1.04</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.83</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H70" t="n">
-        <v>1256.35</v>
+        <v>1239.75</v>
       </c>
       <c r="I70" t="n">
         <v>1254.506917668611</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K70" t="n">
-        <v>2.21</v>
+        <v>0.86</v>
       </c>
       <c r="L70" t="n">
         <v>2.34</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.81</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="H71" t="n">
-        <v>1292.85</v>
+        <v>1331.85</v>
       </c>
       <c r="I71" t="n">
         <v>1300.29079606646</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.28</v>
+        <v>-7.43</v>
       </c>
       <c r="L71" t="n">
-        <v>5.49</v>
+        <v>7.71</v>
       </c>
       <c r="M71" t="n">
         <v>2.39</v>
       </c>
       <c r="N71" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="O71" t="n">
         <v>-1.32</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.86</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="H72" t="n">
-        <v>1294.65</v>
+        <v>1281.65</v>
       </c>
       <c r="I72" t="n">
         <v>1283.324555577123</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.79</v>
+        <v>-3.77</v>
       </c>
       <c r="L72" t="n">
         <v>7.46</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>5.44</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="H73" t="n">
-        <v>1267.7</v>
+        <v>1272.4</v>
       </c>
       <c r="I73" t="n">
         <v>1268.411334214079</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="L73" t="n">
         <v>0.92</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.35</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H74" t="n">
-        <v>1222.45</v>
+        <v>1204.1</v>
       </c>
       <c r="I74" t="n">
         <v>1204.320145698371</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.93</v>
+        <v>-5.37</v>
       </c>
       <c r="L74" t="n">
-        <v>4.88</v>
+        <v>5.68</v>
       </c>
       <c r="M74" t="n">
         <v>0.71</v>
       </c>
       <c r="N74" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="O74" t="n">
         <v>0.37</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>6.07</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45729</v>
+        <v>45733</v>
       </c>
       <c r="H75" t="n">
-        <v>1250.05</v>
+        <v>1269</v>
       </c>
       <c r="I75" t="n">
         <v>1267.459756374949</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.82</v>
+        <v>-5.39</v>
       </c>
       <c r="L75" t="n">
-        <v>4.28</v>
+        <v>5.8</v>
       </c>
       <c r="M75" t="n">
         <v>1.01</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>4.92</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H76" t="n">
-        <v>1335.3</v>
+        <v>1287.55</v>
       </c>
       <c r="I76" t="n">
         <v>1290.247984616654</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K76" t="n">
-        <v>5.22</v>
+        <v>1.46</v>
       </c>
       <c r="L76" t="n">
         <v>1.12</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>2.22</v>
+        <v>3.58</v>
       </c>
       <c r="O76" t="n">
         <v>1.52</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>7.03</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H77" t="n">
-        <v>1356.4</v>
+        <v>1406.7</v>
       </c>
       <c r="I77" t="n">
         <v>1374.422986666851</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.35</v>
+        <v>-9.25</v>
       </c>
       <c r="L77" t="n">
-        <v>5.6</v>
+        <v>9.42</v>
       </c>
       <c r="M77" t="n">
         <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>2.94</v>
+        <v>3.71</v>
       </c>
       <c r="O77" t="n">
         <v>-3.58</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>7.85</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="H78" t="n">
-        <v>1436.6</v>
+        <v>1422</v>
       </c>
       <c r="I78" t="n">
         <v>1429.837914479677</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K78" t="n">
-        <v>2.13</v>
+        <v>1.09</v>
       </c>
       <c r="L78" t="n">
         <v>3.31</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>5</v>
+      </c>
+      <c r="U78" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>4.12</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="H79" t="n">
-        <v>1384.1</v>
+        <v>1398.4</v>
       </c>
       <c r="I79" t="n">
         <v>1398.342708296973</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K79" t="n">
-        <v>2.67</v>
+        <v>1.66</v>
       </c>
       <c r="L79" t="n">
         <v>2.14</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>3.83</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H80" t="n">
-        <v>1382</v>
+        <v>1363.7</v>
       </c>
       <c r="I80" t="n">
         <v>1372.192052737474</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.17</v>
+        <v>-2.48</v>
       </c>
       <c r="L80" t="n">
-        <v>1.61</v>
+        <v>2.74</v>
       </c>
       <c r="M80" t="n">
         <v>0.42</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>5.59</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="H81" t="n">
-        <v>1375</v>
+        <v>1392.2</v>
       </c>
       <c r="I81" t="n">
         <v>1386.132126582457</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.83</v>
+        <v>-2.09</v>
       </c>
       <c r="L81" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="M81" t="n">
         <v>0.86</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>4.36</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="H82" t="n">
-        <v>1342.9</v>
+        <v>1338</v>
       </c>
       <c r="I82" t="n">
         <v>1341.572612184988</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K82" t="n">
-        <v>-3.54</v>
+        <v>-3.89</v>
       </c>
       <c r="L82" t="n">
-        <v>3.89</v>
+        <v>4.04</v>
       </c>
       <c r="M82" t="n">
         <v>0.72</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>3.44</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H83" t="n">
-        <v>1371.5</v>
+        <v>1411.2</v>
       </c>
       <c r="I83" t="n">
         <v>1384.086069334893</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K83" t="n">
-        <v>-2.5</v>
+        <v>-5.47</v>
       </c>
       <c r="L83" t="n">
-        <v>2.8</v>
+        <v>5.65</v>
       </c>
       <c r="M83" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N83" t="n">
-        <v>1.3</v>
+        <v>2.89</v>
       </c>
       <c r="O83" t="n">
         <v>-0.36</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,22 +6215,22 @@
         <v>5.48</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H84" t="n">
-        <v>1375.8</v>
+        <v>1349</v>
       </c>
       <c r="I84" t="n">
         <v>1374.777966918439</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K84" t="n">
-        <v>-2.51</v>
+        <v>-4.41</v>
       </c>
       <c r="L84" t="n">
-        <v>3.63</v>
+        <v>5.08</v>
       </c>
       <c r="M84" t="n">
         <v>0.79</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>6.42</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="H85" t="n">
-        <v>1406.1</v>
+        <v>1430</v>
       </c>
       <c r="I85" t="n">
         <v>1421.532302041554</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K85" t="n">
-        <v>-4.23</v>
+        <v>-6</v>
       </c>
       <c r="L85" t="n">
-        <v>5.04</v>
+        <v>6.23</v>
       </c>
       <c r="M85" t="n">
         <v>4.38</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,28 +6353,28 @@
         <v>6.14</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="H86" t="n">
-        <v>1357.6</v>
+        <v>1313.4</v>
       </c>
       <c r="I86" t="n">
         <v>1346.185015937663</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K86" t="n">
-        <v>-5.06</v>
+        <v>-8.15</v>
       </c>
       <c r="L86" t="n">
-        <v>7.27</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M86" t="n">
         <v>3.49</v>
       </c>
       <c r="N86" t="n">
-        <v>1.85</v>
+        <v>3.26</v>
       </c>
       <c r="O86" t="n">
         <v>1.7</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5379,28 +6422,28 @@
         <v>7.76</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H87" t="n">
-        <v>1245.5</v>
+        <v>1309.2</v>
       </c>
       <c r="I87" t="n">
         <v>1296.075774222187</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K87" t="n">
-        <v>5.17</v>
+        <v>0.32</v>
       </c>
       <c r="L87" t="n">
         <v>3.37</v>
       </c>
       <c r="M87" t="n">
-        <v>1.84</v>
+        <v>5.18</v>
       </c>
       <c r="N87" t="n">
-        <v>2.62</v>
+        <v>5.11</v>
       </c>
       <c r="O87" t="n">
         <v>-3.26</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,25 +6491,25 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H88" t="n">
-        <v>1281</v>
+        <v>1263.4</v>
       </c>
       <c r="I88" t="n">
         <v>1272.046604233287</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K88" t="n">
-        <v>-2.15</v>
+        <v>-3.5</v>
       </c>
       <c r="L88" t="n">
-        <v>2.54</v>
+        <v>3.83</v>
       </c>
       <c r="M88" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="N88" t="n">
         <v>2.13</v>
@@ -5466,7 +6521,19 @@
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5493,22 +6560,22 @@
         <v>7.14</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H89" t="n">
-        <v>1293.3</v>
+        <v>1317</v>
       </c>
       <c r="I89" t="n">
         <v>1303.366076887244</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K89" t="n">
-        <v>-2.37</v>
+        <v>-4.24</v>
       </c>
       <c r="L89" t="n">
-        <v>3.37</v>
+        <v>5.51</v>
       </c>
       <c r="M89" t="n">
         <v>0.86</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5550,19 +6629,19 @@
         <v>6.99</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="H90" t="n">
-        <v>1389.1</v>
+        <v>1384.5</v>
       </c>
       <c r="I90" t="n">
         <v>1386.295787506278</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K90" t="n">
-        <v>5.47</v>
+        <v>5.13</v>
       </c>
       <c r="L90" t="n">
         <v>2.32</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4</v>
+      </c>
+      <c r="U90" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -5607,19 +6698,19 @@
         <v>4.51</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H91" t="n">
-        <v>1342.8</v>
+        <v>1357.5</v>
       </c>
       <c r="I91" t="n">
         <v>1357.409140585881</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K91" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="L91" t="n">
         <v>0.61</v>
@@ -5637,7 +6728,19 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5688,6 +6791,14 @@
       <c r="Q92" t="n">
         <v>15</v>
       </c>
+      <c r="R92" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10646,7 +11757,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="6">
@@ -10656,7 +11767,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -10666,7 +11777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8">
@@ -10676,7 +11787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -10686,7 +11797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="10">
@@ -10696,7 +11807,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95.5</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="11">
@@ -10736,7 +11847,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.09</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="15">
@@ -10746,7 +11857,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16">
@@ -10756,7 +11867,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.74</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="17">
@@ -10766,7 +11877,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="18">
@@ -10776,7 +11887,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37.8</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="19">
@@ -10786,7 +11897,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.96</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="20">
@@ -10796,7 +11907,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.71</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="21">
@@ -10806,7 +11917,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="22">
@@ -10816,7 +11927,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -10826,7 +11937,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -10836,7 +11947,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="25">
@@ -10846,7 +11957,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -10856,7 +11967,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.36</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="27">
@@ -10866,7 +11977,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.76</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="28">
@@ -10876,7 +11987,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
